--- a/받은 데이터/2월/정기 목표(Regular)_SD 외부채널.xlsx
+++ b/받은 데이터/2월/정기 목표(Regular)_SD 외부채널.xlsx
@@ -5,18 +5,21 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\효경\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Python\받은 데이터\2월\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4214E4FF-65E3-474F-8009-3D605C1741E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359183FC-22C0-4013-AFDD-CE5488DBE69C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="1650" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="정기목표" sheetId="1" r:id="rId1"/>
     <sheet name="안내" sheetId="2" r:id="rId2"/>
     <sheet name="목록" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">정기목표!$A$1:$H$179</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
@@ -6817,7 +6820,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -6826,12 +6829,13 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
@@ -7142,7 +7146,7 @@
   <cols>
     <col min="1" max="4" width="15.75" customWidth="1"/>
     <col min="5" max="5" width="21.33203125" customWidth="1"/>
-    <col min="6" max="6" width="21.25" style="8" customWidth="1"/>
+    <col min="6" max="6" width="21.25" style="7" customWidth="1"/>
     <col min="7" max="8" width="15.75" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7162,7 +7166,7 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
@@ -7174,345 +7178,396 @@
     </row>
     <row r="2" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B2" s="5">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="C2" t="s">
         <v>99</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>1806</v>
-      </c>
-      <c r="F2" s="8">
-        <v>90740</v>
+        <v>68</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>1859</v>
+      </c>
+      <c r="F2" s="7">
+        <v>2700000</v>
       </c>
       <c r="G2">
-        <v>13</v>
+        <v>200</v>
+      </c>
+      <c r="H2" t="s">
+        <v>2222</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B3" s="5">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="C3" t="s">
         <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E3" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E3" s="9" t="s">
         <v>1797</v>
       </c>
-      <c r="F3" s="8">
-        <v>48860</v>
+      <c r="F3" s="7">
+        <v>1350000</v>
       </c>
       <c r="G3">
-        <v>7</v>
+        <v>180</v>
+      </c>
+      <c r="H3" t="s">
+        <v>2222</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B4" s="5">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="C4" t="s">
         <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>1884</v>
-      </c>
-      <c r="F4" s="8">
-        <v>149000</v>
+        <v>68</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>1806</v>
+      </c>
+      <c r="F4" s="7">
+        <v>1050000</v>
       </c>
       <c r="G4">
-        <v>10</v>
+        <v>140</v>
+      </c>
+      <c r="H4" t="s">
+        <v>2222</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B5" s="5">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="C5" t="s">
         <v>99</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>1859</v>
-      </c>
-      <c r="F5" s="8">
-        <v>64500</v>
+        <v>68</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>1936</v>
+      </c>
+      <c r="F5" s="7">
+        <v>3402000</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>180</v>
+      </c>
+      <c r="H5" t="s">
+        <v>2222</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B6" s="5">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="C6" t="s">
         <v>99</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>1851</v>
-      </c>
-      <c r="F6" s="8">
-        <v>90300</v>
+        <v>68</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>2047</v>
+      </c>
+      <c r="F6" s="7">
+        <v>1296000</v>
       </c>
       <c r="G6">
-        <v>7</v>
+        <v>200</v>
+      </c>
+      <c r="H6" t="s">
+        <v>2222</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B7" s="5">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="C7" t="s">
         <v>99</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>1937</v>
-      </c>
-      <c r="F7" s="8">
-        <v>874500</v>
+        <v>68</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>2048</v>
+      </c>
+      <c r="F7" s="7">
+        <v>1296000</v>
       </c>
       <c r="G7">
-        <v>55</v>
+        <v>200</v>
+      </c>
+      <c r="H7" t="s">
+        <v>2222</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B8" s="5">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="C8" t="s">
         <v>99</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>1865</v>
-      </c>
-      <c r="F8" s="8">
-        <v>270300</v>
+        <v>68</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>1965</v>
+      </c>
+      <c r="F8" s="7">
+        <v>1296000</v>
       </c>
       <c r="G8">
-        <v>17</v>
+        <v>200</v>
+      </c>
+      <c r="H8" t="s">
+        <v>2222</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B9" s="5">
-        <v>46082</v>
+        <v>46143</v>
       </c>
       <c r="C9" t="s">
         <v>99</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>1921</v>
-      </c>
-      <c r="F9" s="8">
-        <v>129160</v>
+        <v>68</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>1851</v>
+      </c>
+      <c r="F9" s="7">
+        <v>337500</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>25</v>
+      </c>
+      <c r="H9" t="s">
+        <v>2222</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B10" s="5">
-        <v>46082</v>
+        <v>46143</v>
       </c>
       <c r="C10" t="s">
         <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>1917</v>
-      </c>
-      <c r="F10" s="8">
-        <v>1359640</v>
+        <v>68</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>2223</v>
+      </c>
+      <c r="F10" s="7">
+        <v>960000</v>
       </c>
       <c r="G10">
-        <v>38</v>
+        <v>160</v>
+      </c>
+      <c r="H10" t="s">
+        <v>2222</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B11" s="5">
-        <v>46082</v>
+        <v>46143</v>
       </c>
       <c r="C11" t="s">
         <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>1916</v>
-      </c>
-      <c r="F11" s="8">
-        <v>178900</v>
+        <v>68</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>2224</v>
+      </c>
+      <c r="F11" s="7">
+        <v>1020000</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>170</v>
+      </c>
+      <c r="H11" t="s">
+        <v>2222</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B12" s="5">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="C12" t="s">
         <v>99</v>
       </c>
       <c r="D12" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>1915</v>
-      </c>
-      <c r="F12" s="8">
-        <v>30800</v>
+        <v>68</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>1884</v>
+      </c>
+      <c r="F12" s="7">
+        <v>462000</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="H12" t="s">
+        <v>2221</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B13" s="5">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="C13" t="s">
         <v>99</v>
       </c>
       <c r="D13" t="s">
-        <v>41</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>1914</v>
-      </c>
-      <c r="F13" s="8">
-        <v>92400</v>
+        <v>68</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>1859</v>
+      </c>
+      <c r="F13" s="7">
+        <v>810000</v>
       </c>
       <c r="G13">
-        <v>3</v>
+        <v>60</v>
+      </c>
+      <c r="H13" t="s">
+        <v>2221</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B14" s="5">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="C14" t="s">
         <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>41</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>1939</v>
-      </c>
-      <c r="F14" s="8">
-        <v>260100</v>
+        <v>68</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>1797</v>
+      </c>
+      <c r="F14" s="7">
+        <v>225000</v>
       </c>
       <c r="G14">
-        <v>9</v>
+        <v>30</v>
+      </c>
+      <c r="H14" t="s">
+        <v>2221</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B15" s="5">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="C15" t="s">
         <v>99</v>
       </c>
       <c r="D15" t="s">
-        <v>41</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>1867</v>
-      </c>
-      <c r="F15" s="8">
-        <v>202300</v>
+        <v>68</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>1806</v>
+      </c>
+      <c r="F15" s="7">
+        <v>225000</v>
       </c>
       <c r="G15">
-        <v>7</v>
+        <v>30</v>
+      </c>
+      <c r="H15" t="s">
+        <v>2221</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B16" s="5">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="C16" t="s">
         <v>99</v>
       </c>
       <c r="D16" t="s">
-        <v>41</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>1773</v>
-      </c>
-      <c r="F16" s="8">
-        <v>99800</v>
+        <v>68</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>1936</v>
+      </c>
+      <c r="F16" s="7">
+        <v>3024000</v>
       </c>
       <c r="G16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+        <v>160</v>
+      </c>
+      <c r="H16" t="s">
+        <v>2221</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B17" s="5">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="C17" t="s">
         <v>99</v>
       </c>
       <c r="D17" t="s">
-        <v>41</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>1772</v>
-      </c>
-      <c r="F17" s="8">
-        <v>99800</v>
+        <v>68</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>1889</v>
+      </c>
+      <c r="F17" s="7">
+        <v>194400</v>
       </c>
       <c r="G17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+        <v>30</v>
+      </c>
+      <c r="H17" t="s">
+        <v>2221</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B18" s="5">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="C18" t="s">
         <v>99</v>
       </c>
       <c r="D18" t="s">
-        <v>41</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>1774</v>
-      </c>
-      <c r="F18" s="8">
-        <v>99800</v>
+        <v>68</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>2047</v>
+      </c>
+      <c r="F18" s="7">
+        <v>453600</v>
       </c>
       <c r="G18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.45">
+        <v>70</v>
+      </c>
+      <c r="H18" t="s">
+        <v>2221</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B19" s="5">
         <v>46113</v>
       </c>
@@ -7520,19 +7575,22 @@
         <v>99</v>
       </c>
       <c r="D19" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="E19" t="s">
-        <v>1806</v>
-      </c>
-      <c r="F19" s="8">
-        <v>90740</v>
+        <v>2048</v>
+      </c>
+      <c r="F19" s="7">
+        <v>453600</v>
       </c>
       <c r="G19">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.45">
+        <v>70</v>
+      </c>
+      <c r="H19" t="s">
+        <v>2221</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B20" s="5">
         <v>46113</v>
       </c>
@@ -7540,161 +7598,185 @@
         <v>99</v>
       </c>
       <c r="D20" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="E20" t="s">
-        <v>1797</v>
-      </c>
-      <c r="F20" s="8">
-        <v>48860</v>
+        <v>1965</v>
+      </c>
+      <c r="F20" s="7">
+        <v>453600</v>
       </c>
       <c r="G20">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.45">
+        <v>70</v>
+      </c>
+      <c r="H20" t="s">
+        <v>2221</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B21" s="5">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="C21" t="s">
         <v>99</v>
       </c>
       <c r="D21" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="E21" t="s">
-        <v>1884</v>
-      </c>
-      <c r="F21" s="8">
-        <v>29800</v>
+        <v>1851</v>
+      </c>
+      <c r="F21" s="7">
+        <v>135000</v>
       </c>
       <c r="G21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.45">
+        <v>10</v>
+      </c>
+      <c r="H21" t="s">
+        <v>2221</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B22" s="5">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="C22" t="s">
         <v>99</v>
       </c>
       <c r="D22" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="E22" t="s">
-        <v>1859</v>
-      </c>
-      <c r="F22" s="8">
-        <v>64500</v>
+        <v>2223</v>
+      </c>
+      <c r="F22" s="7">
+        <v>300000</v>
       </c>
       <c r="G22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.45">
+        <v>50</v>
+      </c>
+      <c r="H22" t="s">
+        <v>2221</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B23" s="5">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="C23" t="s">
         <v>99</v>
       </c>
       <c r="D23" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="E23" t="s">
-        <v>1851</v>
-      </c>
-      <c r="F23" s="8">
-        <v>90300</v>
+        <v>2224</v>
+      </c>
+      <c r="F23" s="7">
+        <v>150000</v>
       </c>
       <c r="G23">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="H23" t="s">
+        <v>2221</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B24" s="5">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="C24" t="s">
         <v>99</v>
       </c>
       <c r="D24" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="E24" t="s">
-        <v>1937</v>
-      </c>
-      <c r="F24" s="8">
-        <v>477000</v>
+        <v>1843</v>
+      </c>
+      <c r="F24" s="7">
+        <v>247500</v>
       </c>
       <c r="G24">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.45">
+        <v>5</v>
+      </c>
+      <c r="H24" t="s">
+        <v>2221</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B25" s="5">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="C25" t="s">
         <v>99</v>
       </c>
       <c r="D25" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="E25" t="s">
-        <v>1865</v>
-      </c>
-      <c r="F25" s="8">
-        <v>270300</v>
+        <v>1781</v>
+      </c>
+      <c r="F25" s="7">
+        <v>157500</v>
       </c>
       <c r="G25">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.45">
+        <v>5</v>
+      </c>
+      <c r="H25" t="s">
+        <v>2221</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B26" s="5">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="C26" t="s">
         <v>99</v>
       </c>
       <c r="D26" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="E26" t="s">
-        <v>1921</v>
-      </c>
-      <c r="F26" s="8">
-        <v>129160</v>
+        <v>2046</v>
+      </c>
+      <c r="F26" s="7">
+        <v>94500</v>
       </c>
       <c r="G26">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.45">
+        <v>3</v>
+      </c>
+      <c r="H26" t="s">
+        <v>2221</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B27" s="5">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="C27" t="s">
         <v>99</v>
       </c>
       <c r="D27" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="E27" t="s">
-        <v>1917</v>
-      </c>
-      <c r="F27" s="8">
-        <v>1359640</v>
+        <v>1923</v>
+      </c>
+      <c r="F27" s="7">
+        <v>437600</v>
       </c>
       <c r="G27">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+      <c r="H27" t="s">
+        <v>2221</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B28" s="5">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="C28" t="s">
         <v>99</v>
@@ -7702,19 +7784,19 @@
       <c r="D28" t="s">
         <v>41</v>
       </c>
-      <c r="E28" t="s">
-        <v>1916</v>
-      </c>
-      <c r="F28" s="8">
-        <v>178900</v>
+      <c r="E28" s="10" t="s">
+        <v>1806</v>
+      </c>
+      <c r="F28" s="7">
+        <v>90740</v>
       </c>
       <c r="G28">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.45">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B29" s="5">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="C29" t="s">
         <v>99</v>
@@ -7722,19 +7804,19 @@
       <c r="D29" t="s">
         <v>41</v>
       </c>
-      <c r="E29" t="s">
-        <v>1915</v>
-      </c>
-      <c r="F29" s="8">
-        <v>30800</v>
+      <c r="E29" s="10" t="s">
+        <v>1797</v>
+      </c>
+      <c r="F29" s="7">
+        <v>48860</v>
       </c>
       <c r="G29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.45">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B30" s="5">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="C30" t="s">
         <v>99</v>
@@ -7742,19 +7824,19 @@
       <c r="D30" t="s">
         <v>41</v>
       </c>
-      <c r="E30" t="s">
-        <v>1914</v>
-      </c>
-      <c r="F30" s="8">
-        <v>92400</v>
+      <c r="E30" s="10" t="s">
+        <v>1884</v>
+      </c>
+      <c r="F30" s="7">
+        <v>149000</v>
       </c>
       <c r="G30">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B31" s="5">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="C31" t="s">
         <v>99</v>
@@ -7762,19 +7844,19 @@
       <c r="D31" t="s">
         <v>41</v>
       </c>
-      <c r="E31" t="s">
-        <v>1939</v>
-      </c>
-      <c r="F31" s="8">
-        <v>260100</v>
+      <c r="E31" s="10" t="s">
+        <v>1859</v>
+      </c>
+      <c r="F31" s="7">
+        <v>64500</v>
       </c>
       <c r="G31">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B32" s="5">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="C32" t="s">
         <v>99</v>
@@ -7782,11 +7864,11 @@
       <c r="D32" t="s">
         <v>41</v>
       </c>
-      <c r="E32" t="s">
-        <v>1867</v>
-      </c>
-      <c r="F32" s="8">
-        <v>202300</v>
+      <c r="E32" s="10" t="s">
+        <v>1851</v>
+      </c>
+      <c r="F32" s="7">
+        <v>90300</v>
       </c>
       <c r="G32">
         <v>7</v>
@@ -7794,7 +7876,7 @@
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B33" s="5">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="C33" t="s">
         <v>99</v>
@@ -7802,19 +7884,19 @@
       <c r="D33" t="s">
         <v>41</v>
       </c>
-      <c r="E33" t="s">
-        <v>1773</v>
-      </c>
-      <c r="F33" s="8">
-        <v>99800</v>
+      <c r="E33" s="10" t="s">
+        <v>1937</v>
+      </c>
+      <c r="F33" s="7">
+        <v>874500</v>
       </c>
       <c r="G33">
-        <v>2</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B34" s="5">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="C34" t="s">
         <v>99</v>
@@ -7822,19 +7904,19 @@
       <c r="D34" t="s">
         <v>41</v>
       </c>
-      <c r="E34" t="s">
-        <v>1772</v>
-      </c>
-      <c r="F34" s="8">
-        <v>99800</v>
+      <c r="E34" s="10" t="s">
+        <v>1865</v>
+      </c>
+      <c r="F34" s="7">
+        <v>270300</v>
       </c>
       <c r="G34">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B35" s="5">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="C35" t="s">
         <v>99</v>
@@ -7842,11 +7924,11 @@
       <c r="D35" t="s">
         <v>41</v>
       </c>
-      <c r="E35" t="s">
-        <v>1774</v>
-      </c>
-      <c r="F35" s="8">
-        <v>99800</v>
+      <c r="E35" s="10" t="s">
+        <v>1921</v>
+      </c>
+      <c r="F35" s="7">
+        <v>129160</v>
       </c>
       <c r="G35">
         <v>2</v>
@@ -7854,7 +7936,7 @@
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B36" s="5">
-        <v>46143</v>
+        <v>46082</v>
       </c>
       <c r="C36" t="s">
         <v>99</v>
@@ -7862,19 +7944,19 @@
       <c r="D36" t="s">
         <v>41</v>
       </c>
-      <c r="E36" t="s">
-        <v>1806</v>
-      </c>
-      <c r="F36" s="8">
-        <v>90740</v>
+      <c r="E36" s="10" t="s">
+        <v>1917</v>
+      </c>
+      <c r="F36" s="7">
+        <v>1359640</v>
       </c>
       <c r="G36">
-        <v>13</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B37" s="5">
-        <v>46143</v>
+        <v>46082</v>
       </c>
       <c r="C37" t="s">
         <v>99</v>
@@ -7882,19 +7964,19 @@
       <c r="D37" t="s">
         <v>41</v>
       </c>
-      <c r="E37" t="s">
-        <v>1797</v>
-      </c>
-      <c r="F37" s="8">
-        <v>48860</v>
+      <c r="E37" s="10" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F37" s="7">
+        <v>178900</v>
       </c>
       <c r="G37">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B38" s="5">
-        <v>46143</v>
+        <v>46082</v>
       </c>
       <c r="C38" t="s">
         <v>99</v>
@@ -7902,19 +7984,19 @@
       <c r="D38" t="s">
         <v>41</v>
       </c>
-      <c r="E38" t="s">
-        <v>1884</v>
-      </c>
-      <c r="F38" s="8">
-        <v>29800</v>
+      <c r="E38" s="10" t="s">
+        <v>1915</v>
+      </c>
+      <c r="F38" s="7">
+        <v>30800</v>
       </c>
       <c r="G38">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B39" s="5">
-        <v>46143</v>
+        <v>46082</v>
       </c>
       <c r="C39" t="s">
         <v>99</v>
@@ -7922,19 +8004,19 @@
       <c r="D39" t="s">
         <v>41</v>
       </c>
-      <c r="E39" t="s">
-        <v>1859</v>
-      </c>
-      <c r="F39" s="8">
-        <v>64500</v>
+      <c r="E39" s="10" t="s">
+        <v>1914</v>
+      </c>
+      <c r="F39" s="7">
+        <v>92400</v>
       </c>
       <c r="G39">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B40" s="5">
-        <v>46143</v>
+        <v>46082</v>
       </c>
       <c r="C40" t="s">
         <v>99</v>
@@ -7942,19 +8024,19 @@
       <c r="D40" t="s">
         <v>41</v>
       </c>
-      <c r="E40" t="s">
-        <v>1851</v>
-      </c>
-      <c r="F40" s="8">
-        <v>90300</v>
+      <c r="E40" s="10" t="s">
+        <v>1939</v>
+      </c>
+      <c r="F40" s="7">
+        <v>260100</v>
       </c>
       <c r="G40">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B41" s="5">
-        <v>46143</v>
+        <v>46082</v>
       </c>
       <c r="C41" t="s">
         <v>99</v>
@@ -7962,19 +8044,19 @@
       <c r="D41" t="s">
         <v>41</v>
       </c>
-      <c r="E41" t="s">
-        <v>1937</v>
-      </c>
-      <c r="F41" s="8">
-        <v>556500</v>
+      <c r="E41" s="10" t="s">
+        <v>1867</v>
+      </c>
+      <c r="F41" s="7">
+        <v>202300</v>
       </c>
       <c r="G41">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B42" s="5">
-        <v>46143</v>
+        <v>46082</v>
       </c>
       <c r="C42" t="s">
         <v>99</v>
@@ -7982,19 +8064,19 @@
       <c r="D42" t="s">
         <v>41</v>
       </c>
-      <c r="E42" t="s">
-        <v>1865</v>
-      </c>
-      <c r="F42" s="8">
-        <v>270300</v>
+      <c r="E42" s="10" t="s">
+        <v>1773</v>
+      </c>
+      <c r="F42" s="7">
+        <v>99800</v>
       </c>
       <c r="G42">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B43" s="5">
-        <v>46143</v>
+        <v>46082</v>
       </c>
       <c r="C43" t="s">
         <v>99</v>
@@ -8002,11 +8084,11 @@
       <c r="D43" t="s">
         <v>41</v>
       </c>
-      <c r="E43" t="s">
-        <v>1921</v>
-      </c>
-      <c r="F43" s="8">
-        <v>129160</v>
+      <c r="E43" s="10" t="s">
+        <v>1772</v>
+      </c>
+      <c r="F43" s="7">
+        <v>99800</v>
       </c>
       <c r="G43">
         <v>2</v>
@@ -8014,7 +8096,7 @@
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B44" s="5">
-        <v>46143</v>
+        <v>46082</v>
       </c>
       <c r="C44" t="s">
         <v>99</v>
@@ -8022,19 +8104,19 @@
       <c r="D44" t="s">
         <v>41</v>
       </c>
-      <c r="E44" t="s">
-        <v>1917</v>
-      </c>
-      <c r="F44" s="8">
-        <v>894500</v>
+      <c r="E44" s="10" t="s">
+        <v>1774</v>
+      </c>
+      <c r="F44" s="7">
+        <v>99800</v>
       </c>
       <c r="G44">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B45" s="5">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="C45" t="s">
         <v>99</v>
@@ -8043,18 +8125,18 @@
         <v>41</v>
       </c>
       <c r="E45" t="s">
-        <v>1916</v>
-      </c>
-      <c r="F45" s="8">
-        <v>178900</v>
+        <v>1806</v>
+      </c>
+      <c r="F45" s="7">
+        <v>90740</v>
       </c>
       <c r="G45">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B46" s="5">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="C46" t="s">
         <v>99</v>
@@ -8063,18 +8145,18 @@
         <v>41</v>
       </c>
       <c r="E46" t="s">
-        <v>1915</v>
-      </c>
-      <c r="F46" s="8">
-        <v>30800</v>
+        <v>1797</v>
+      </c>
+      <c r="F46" s="7">
+        <v>48860</v>
       </c>
       <c r="G46">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B47" s="5">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="C47" t="s">
         <v>99</v>
@@ -8083,18 +8165,18 @@
         <v>41</v>
       </c>
       <c r="E47" t="s">
-        <v>1914</v>
-      </c>
-      <c r="F47" s="8">
-        <v>92400</v>
+        <v>1884</v>
+      </c>
+      <c r="F47" s="7">
+        <v>29800</v>
       </c>
       <c r="G47">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B48" s="5">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="C48" t="s">
         <v>99</v>
@@ -8103,18 +8185,18 @@
         <v>41</v>
       </c>
       <c r="E48" t="s">
-        <v>1939</v>
-      </c>
-      <c r="F48" s="8">
-        <v>260100</v>
+        <v>1859</v>
+      </c>
+      <c r="F48" s="7">
+        <v>64500</v>
       </c>
       <c r="G48">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B49" s="5">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="C49" t="s">
         <v>99</v>
@@ -8123,10 +8205,10 @@
         <v>41</v>
       </c>
       <c r="E49" t="s">
-        <v>1867</v>
-      </c>
-      <c r="F49" s="8">
-        <v>202300</v>
+        <v>1851</v>
+      </c>
+      <c r="F49" s="7">
+        <v>90300</v>
       </c>
       <c r="G49">
         <v>7</v>
@@ -8134,7 +8216,7 @@
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B50" s="5">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="C50" t="s">
         <v>99</v>
@@ -8143,18 +8225,18 @@
         <v>41</v>
       </c>
       <c r="E50" t="s">
-        <v>1773</v>
-      </c>
-      <c r="F50" s="8">
-        <v>49900</v>
+        <v>1937</v>
+      </c>
+      <c r="F50" s="7">
+        <v>477000</v>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B51" s="5">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="C51" t="s">
         <v>99</v>
@@ -8163,18 +8245,18 @@
         <v>41</v>
       </c>
       <c r="E51" t="s">
-        <v>1772</v>
-      </c>
-      <c r="F51" s="8">
-        <v>49900</v>
+        <v>1865</v>
+      </c>
+      <c r="F51" s="7">
+        <v>270300</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B52" s="5">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="C52" t="s">
         <v>99</v>
@@ -8183,18 +8265,18 @@
         <v>41</v>
       </c>
       <c r="E52" t="s">
-        <v>1774</v>
-      </c>
-      <c r="F52" s="8">
-        <v>49900</v>
+        <v>1921</v>
+      </c>
+      <c r="F52" s="7">
+        <v>129160</v>
       </c>
       <c r="G52">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B53" s="5">
-        <v>46174</v>
+        <v>46113</v>
       </c>
       <c r="C53" t="s">
         <v>99</v>
@@ -8203,18 +8285,18 @@
         <v>41</v>
       </c>
       <c r="E53" t="s">
-        <v>1806</v>
-      </c>
-      <c r="F53" s="8">
-        <v>90740</v>
+        <v>1917</v>
+      </c>
+      <c r="F53" s="7">
+        <v>1359640</v>
       </c>
       <c r="G53">
-        <v>13</v>
+        <v>38</v>
       </c>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B54" s="5">
-        <v>46174</v>
+        <v>46113</v>
       </c>
       <c r="C54" t="s">
         <v>99</v>
@@ -8223,18 +8305,18 @@
         <v>41</v>
       </c>
       <c r="E54" t="s">
-        <v>1797</v>
-      </c>
-      <c r="F54" s="8">
-        <v>48860</v>
+        <v>1916</v>
+      </c>
+      <c r="F54" s="7">
+        <v>178900</v>
       </c>
       <c r="G54">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B55" s="5">
-        <v>46174</v>
+        <v>46113</v>
       </c>
       <c r="C55" t="s">
         <v>99</v>
@@ -8243,18 +8325,18 @@
         <v>41</v>
       </c>
       <c r="E55" t="s">
-        <v>1884</v>
-      </c>
-      <c r="F55" s="8">
-        <v>29800</v>
+        <v>1915</v>
+      </c>
+      <c r="F55" s="7">
+        <v>30800</v>
       </c>
       <c r="G55">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B56" s="5">
-        <v>46174</v>
+        <v>46113</v>
       </c>
       <c r="C56" t="s">
         <v>99</v>
@@ -8263,18 +8345,18 @@
         <v>41</v>
       </c>
       <c r="E56" t="s">
-        <v>1859</v>
-      </c>
-      <c r="F56" s="8">
-        <v>64500</v>
+        <v>1914</v>
+      </c>
+      <c r="F56" s="7">
+        <v>92400</v>
       </c>
       <c r="G56">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B57" s="5">
-        <v>46174</v>
+        <v>46113</v>
       </c>
       <c r="C57" t="s">
         <v>99</v>
@@ -8283,18 +8365,18 @@
         <v>41</v>
       </c>
       <c r="E57" t="s">
-        <v>1851</v>
-      </c>
-      <c r="F57" s="8">
-        <v>90300</v>
+        <v>1939</v>
+      </c>
+      <c r="F57" s="7">
+        <v>260100</v>
       </c>
       <c r="G57">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B58" s="5">
-        <v>46174</v>
+        <v>46113</v>
       </c>
       <c r="C58" t="s">
         <v>99</v>
@@ -8303,18 +8385,18 @@
         <v>41</v>
       </c>
       <c r="E58" t="s">
-        <v>1937</v>
-      </c>
-      <c r="F58" s="8">
-        <v>556500</v>
+        <v>1867</v>
+      </c>
+      <c r="F58" s="7">
+        <v>202300</v>
       </c>
       <c r="G58">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B59" s="5">
-        <v>46174</v>
+        <v>46113</v>
       </c>
       <c r="C59" t="s">
         <v>99</v>
@@ -8323,18 +8405,18 @@
         <v>41</v>
       </c>
       <c r="E59" t="s">
-        <v>1865</v>
-      </c>
-      <c r="F59" s="8">
-        <v>270300</v>
+        <v>1773</v>
+      </c>
+      <c r="F59" s="7">
+        <v>99800</v>
       </c>
       <c r="G59">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B60" s="5">
-        <v>46174</v>
+        <v>46113</v>
       </c>
       <c r="C60" t="s">
         <v>99</v>
@@ -8343,10 +8425,10 @@
         <v>41</v>
       </c>
       <c r="E60" t="s">
-        <v>1921</v>
-      </c>
-      <c r="F60" s="8">
-        <v>129160</v>
+        <v>1772</v>
+      </c>
+      <c r="F60" s="7">
+        <v>99800</v>
       </c>
       <c r="G60">
         <v>2</v>
@@ -8354,7 +8436,7 @@
     </row>
     <row r="61" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B61" s="5">
-        <v>46174</v>
+        <v>46113</v>
       </c>
       <c r="C61" t="s">
         <v>99</v>
@@ -8363,18 +8445,18 @@
         <v>41</v>
       </c>
       <c r="E61" t="s">
-        <v>1917</v>
-      </c>
-      <c r="F61" s="8">
-        <v>1252300</v>
+        <v>1774</v>
+      </c>
+      <c r="F61" s="7">
+        <v>99800</v>
       </c>
       <c r="G61">
-        <v>35</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B62" s="5">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="C62" t="s">
         <v>99</v>
@@ -8383,18 +8465,18 @@
         <v>41</v>
       </c>
       <c r="E62" t="s">
-        <v>1916</v>
-      </c>
-      <c r="F62" s="8">
-        <v>357800</v>
+        <v>1806</v>
+      </c>
+      <c r="F62" s="7">
+        <v>90740</v>
       </c>
       <c r="G62">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="63" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B63" s="5">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="C63" t="s">
         <v>99</v>
@@ -8403,18 +8485,18 @@
         <v>41</v>
       </c>
       <c r="E63" t="s">
-        <v>1915</v>
-      </c>
-      <c r="F63" s="8">
-        <v>30800</v>
+        <v>1797</v>
+      </c>
+      <c r="F63" s="7">
+        <v>48860</v>
       </c>
       <c r="G63">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B64" s="5">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="C64" t="s">
         <v>99</v>
@@ -8423,18 +8505,18 @@
         <v>41</v>
       </c>
       <c r="E64" t="s">
-        <v>1914</v>
-      </c>
-      <c r="F64" s="8">
-        <v>92400</v>
+        <v>1884</v>
+      </c>
+      <c r="F64" s="7">
+        <v>29800</v>
       </c>
       <c r="G64">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B65" s="5">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="C65" t="s">
         <v>99</v>
@@ -8443,18 +8525,18 @@
         <v>41</v>
       </c>
       <c r="E65" t="s">
-        <v>1939</v>
-      </c>
-      <c r="F65" s="8">
-        <v>260100</v>
+        <v>1859</v>
+      </c>
+      <c r="F65" s="7">
+        <v>64500</v>
       </c>
       <c r="G65">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B66" s="5">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="C66" t="s">
         <v>99</v>
@@ -8463,10 +8545,10 @@
         <v>41</v>
       </c>
       <c r="E66" t="s">
-        <v>1867</v>
-      </c>
-      <c r="F66" s="8">
-        <v>202300</v>
+        <v>1851</v>
+      </c>
+      <c r="F66" s="7">
+        <v>90300</v>
       </c>
       <c r="G66">
         <v>7</v>
@@ -8474,7 +8556,7 @@
     </row>
     <row r="67" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B67" s="5">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="C67" t="s">
         <v>99</v>
@@ -8483,18 +8565,18 @@
         <v>41</v>
       </c>
       <c r="E67" t="s">
-        <v>1773</v>
-      </c>
-      <c r="F67" s="8">
-        <v>49900</v>
+        <v>1937</v>
+      </c>
+      <c r="F67" s="7">
+        <v>556500</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>35</v>
       </c>
     </row>
     <row r="68" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B68" s="5">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="C68" t="s">
         <v>99</v>
@@ -8503,18 +8585,18 @@
         <v>41</v>
       </c>
       <c r="E68" t="s">
-        <v>1772</v>
-      </c>
-      <c r="F68" s="8">
-        <v>49900</v>
+        <v>1865</v>
+      </c>
+      <c r="F68" s="7">
+        <v>270300</v>
       </c>
       <c r="G68">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="69" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B69" s="5">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="C69" t="s">
         <v>99</v>
@@ -8523,270 +8605,270 @@
         <v>41</v>
       </c>
       <c r="E69" t="s">
-        <v>1774</v>
-      </c>
-      <c r="F69" s="8">
-        <v>49900</v>
+        <v>1921</v>
+      </c>
+      <c r="F69" s="7">
+        <v>129160</v>
       </c>
       <c r="G69">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B70" s="5">
-        <v>46082</v>
+        <v>46143</v>
       </c>
       <c r="C70" t="s">
         <v>99</v>
       </c>
       <c r="D70" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E70" t="s">
-        <v>1884</v>
-      </c>
-      <c r="F70" s="8">
-        <v>44700</v>
+        <v>1917</v>
+      </c>
+      <c r="F70" s="7">
+        <v>894500</v>
       </c>
       <c r="G70">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="71" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B71" s="5">
-        <v>46082</v>
+        <v>46143</v>
       </c>
       <c r="C71" t="s">
         <v>99</v>
       </c>
       <c r="D71" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E71" t="s">
-        <v>1865</v>
-      </c>
-      <c r="F71" s="8">
-        <v>556500</v>
+        <v>1916</v>
+      </c>
+      <c r="F71" s="7">
+        <v>178900</v>
       </c>
       <c r="G71">
-        <v>35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B72" s="5">
-        <v>46082</v>
+        <v>46143</v>
       </c>
       <c r="C72" t="s">
         <v>99</v>
       </c>
       <c r="D72" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E72" t="s">
-        <v>1937</v>
-      </c>
-      <c r="F72" s="8">
-        <v>954000</v>
+        <v>1915</v>
+      </c>
+      <c r="F72" s="7">
+        <v>30800</v>
       </c>
       <c r="G72">
-        <v>60</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B73" s="5">
-        <v>46082</v>
+        <v>46143</v>
       </c>
       <c r="C73" t="s">
         <v>99</v>
       </c>
       <c r="D73" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E73" t="s">
-        <v>1851</v>
-      </c>
-      <c r="F73" s="8">
-        <v>64500</v>
+        <v>1914</v>
+      </c>
+      <c r="F73" s="7">
+        <v>92400</v>
       </c>
       <c r="G73">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B74" s="5">
-        <v>46082</v>
+        <v>46143</v>
       </c>
       <c r="C74" t="s">
         <v>99</v>
       </c>
       <c r="D74" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E74" t="s">
-        <v>1859</v>
-      </c>
-      <c r="F74" s="8">
-        <v>38700</v>
+        <v>1939</v>
+      </c>
+      <c r="F74" s="7">
+        <v>260100</v>
       </c>
       <c r="G74">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="75" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B75" s="5">
-        <v>46082</v>
+        <v>46143</v>
       </c>
       <c r="C75" t="s">
         <v>99</v>
       </c>
       <c r="D75" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E75" t="s">
         <v>1867</v>
       </c>
-      <c r="F75" s="8">
-        <v>231200</v>
+      <c r="F75" s="7">
+        <v>202300</v>
       </c>
       <c r="G75">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B76" s="5">
-        <v>46082</v>
+        <v>46143</v>
       </c>
       <c r="C76" t="s">
         <v>99</v>
       </c>
       <c r="D76" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E76" t="s">
-        <v>1797</v>
-      </c>
-      <c r="F76" s="8">
-        <v>34900</v>
+        <v>1773</v>
+      </c>
+      <c r="F76" s="7">
+        <v>49900</v>
       </c>
       <c r="G76">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B77" s="5">
-        <v>46082</v>
+        <v>46143</v>
       </c>
       <c r="C77" t="s">
         <v>99</v>
       </c>
       <c r="D77" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E77" t="s">
-        <v>1806</v>
-      </c>
-      <c r="F77" s="8">
-        <v>34900</v>
+        <v>1772</v>
+      </c>
+      <c r="F77" s="7">
+        <v>49900</v>
       </c>
       <c r="G77">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B78" s="5">
-        <v>46082</v>
+        <v>46143</v>
       </c>
       <c r="C78" t="s">
         <v>99</v>
       </c>
       <c r="D78" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E78" t="s">
-        <v>1939</v>
-      </c>
-      <c r="F78" s="8">
-        <v>202300</v>
+        <v>1774</v>
+      </c>
+      <c r="F78" s="7">
+        <v>49900</v>
       </c>
       <c r="G78">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B79" s="5">
-        <v>46082</v>
+        <v>46174</v>
       </c>
       <c r="C79" t="s">
         <v>99</v>
       </c>
       <c r="D79" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E79" t="s">
-        <v>1913</v>
-      </c>
-      <c r="F79" s="8">
-        <v>516800</v>
+        <v>1806</v>
+      </c>
+      <c r="F79" s="7">
+        <v>90740</v>
       </c>
       <c r="G79">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="80" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B80" s="5">
-        <v>46082</v>
+        <v>46174</v>
       </c>
       <c r="C80" t="s">
         <v>99</v>
       </c>
       <c r="D80" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E80" t="s">
-        <v>1906</v>
-      </c>
-      <c r="F80" s="8">
-        <v>70700</v>
+        <v>1797</v>
+      </c>
+      <c r="F80" s="7">
+        <v>48860</v>
       </c>
       <c r="G80">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B81" s="5">
-        <v>46082</v>
+        <v>46174</v>
       </c>
       <c r="C81" t="s">
         <v>99</v>
       </c>
       <c r="D81" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E81" t="s">
-        <v>1924</v>
-      </c>
-      <c r="F81" s="8">
-        <v>228800</v>
+        <v>1884</v>
+      </c>
+      <c r="F81" s="7">
+        <v>29800</v>
       </c>
       <c r="G81">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B82" s="5">
-        <v>46082</v>
+        <v>46174</v>
       </c>
       <c r="C82" t="s">
         <v>99</v>
       </c>
       <c r="D82" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E82" t="s">
-        <v>1925</v>
-      </c>
-      <c r="F82" s="8">
-        <v>114400</v>
+        <v>1859</v>
+      </c>
+      <c r="F82" s="7">
+        <v>64500</v>
       </c>
       <c r="G82">
         <v>5</v>
@@ -8794,159 +8876,159 @@
     </row>
     <row r="83" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B83" s="5">
-        <v>46082</v>
+        <v>46174</v>
       </c>
       <c r="C83" t="s">
         <v>99</v>
       </c>
       <c r="D83" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E83" t="s">
-        <v>1926</v>
-      </c>
-      <c r="F83" s="8">
-        <v>74800</v>
+        <v>1851</v>
+      </c>
+      <c r="F83" s="7">
+        <v>90300</v>
       </c>
       <c r="G83">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B84" s="5">
-        <v>46082</v>
+        <v>46174</v>
       </c>
       <c r="C84" t="s">
         <v>99</v>
       </c>
       <c r="D84" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E84" t="s">
-        <v>1923</v>
-      </c>
-      <c r="F84" s="8">
-        <v>149660</v>
+        <v>1937</v>
+      </c>
+      <c r="F84" s="7">
+        <v>556500</v>
       </c>
       <c r="G84">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="85" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B85" s="5">
-        <v>46082</v>
+        <v>46174</v>
       </c>
       <c r="C85" t="s">
         <v>99</v>
       </c>
       <c r="D85" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E85" t="s">
-        <v>1800</v>
-      </c>
-      <c r="F85" s="8">
-        <v>104700</v>
+        <v>1865</v>
+      </c>
+      <c r="F85" s="7">
+        <v>270300</v>
       </c>
       <c r="G85">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="86" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B86" s="5">
-        <v>46082</v>
+        <v>46174</v>
       </c>
       <c r="C86" t="s">
         <v>99</v>
       </c>
       <c r="D86" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E86" t="s">
-        <v>1947</v>
-      </c>
-      <c r="F86" s="8">
-        <v>756000</v>
+        <v>1921</v>
+      </c>
+      <c r="F86" s="7">
+        <v>129160</v>
       </c>
       <c r="G86">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B87" s="5">
-        <v>46082</v>
+        <v>46174</v>
       </c>
       <c r="C87" t="s">
         <v>99</v>
       </c>
       <c r="D87" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E87" t="s">
-        <v>1930</v>
-      </c>
-      <c r="F87" s="8">
-        <v>388200</v>
+        <v>1917</v>
+      </c>
+      <c r="F87" s="7">
+        <v>1252300</v>
       </c>
       <c r="G87">
-        <v>15</v>
+        <v>35</v>
       </c>
     </row>
     <row r="88" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B88" s="5">
-        <v>46082</v>
+        <v>46174</v>
       </c>
       <c r="C88" t="s">
         <v>99</v>
       </c>
       <c r="D88" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E88" t="s">
-        <v>1931</v>
-      </c>
-      <c r="F88" s="8">
-        <v>388200</v>
+        <v>1916</v>
+      </c>
+      <c r="F88" s="7">
+        <v>357800</v>
       </c>
       <c r="G88">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="89" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B89" s="5">
-        <v>46082</v>
+        <v>46174</v>
       </c>
       <c r="C89" t="s">
         <v>99</v>
       </c>
       <c r="D89" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E89" t="s">
-        <v>1932</v>
-      </c>
-      <c r="F89" s="8">
-        <v>636000</v>
+        <v>1915</v>
+      </c>
+      <c r="F89" s="7">
+        <v>30800</v>
       </c>
       <c r="G89">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B90" s="5">
-        <v>46113</v>
+        <v>46174</v>
       </c>
       <c r="C90" t="s">
         <v>99</v>
       </c>
       <c r="D90" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E90" t="s">
-        <v>1884</v>
-      </c>
-      <c r="F90" s="8">
-        <v>44700</v>
+        <v>1914</v>
+      </c>
+      <c r="F90" s="7">
+        <v>92400</v>
       </c>
       <c r="G90">
         <v>3</v>
@@ -8954,107 +9036,107 @@
     </row>
     <row r="91" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B91" s="5">
-        <v>46113</v>
+        <v>46174</v>
       </c>
       <c r="C91" t="s">
         <v>99</v>
       </c>
       <c r="D91" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E91" t="s">
-        <v>1865</v>
-      </c>
-      <c r="F91" s="8">
-        <v>795000</v>
+        <v>1939</v>
+      </c>
+      <c r="F91" s="7">
+        <v>260100</v>
       </c>
       <c r="G91">
-        <v>50</v>
+        <v>9</v>
       </c>
     </row>
     <row r="92" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B92" s="5">
-        <v>46113</v>
+        <v>46174</v>
       </c>
       <c r="C92" t="s">
         <v>99</v>
       </c>
       <c r="D92" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E92" t="s">
-        <v>1937</v>
-      </c>
-      <c r="F92" s="8">
-        <v>1272000</v>
+        <v>1867</v>
+      </c>
+      <c r="F92" s="7">
+        <v>202300</v>
       </c>
       <c r="G92">
-        <v>80</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B93" s="5">
-        <v>46113</v>
+        <v>46174</v>
       </c>
       <c r="C93" t="s">
         <v>99</v>
       </c>
       <c r="D93" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E93" t="s">
-        <v>1851</v>
-      </c>
-      <c r="F93" s="8">
-        <v>64500</v>
+        <v>1773</v>
+      </c>
+      <c r="F93" s="7">
+        <v>49900</v>
       </c>
       <c r="G93">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B94" s="5">
-        <v>46113</v>
+        <v>46174</v>
       </c>
       <c r="C94" t="s">
         <v>99</v>
       </c>
       <c r="D94" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E94" t="s">
-        <v>1859</v>
-      </c>
-      <c r="F94" s="8">
-        <v>38700</v>
+        <v>1772</v>
+      </c>
+      <c r="F94" s="7">
+        <v>49900</v>
       </c>
       <c r="G94">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B95" s="5">
-        <v>46113</v>
+        <v>46174</v>
       </c>
       <c r="C95" t="s">
         <v>99</v>
       </c>
       <c r="D95" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="E95" t="s">
-        <v>1867</v>
-      </c>
-      <c r="F95" s="8">
-        <v>231200</v>
+        <v>1774</v>
+      </c>
+      <c r="F95" s="7">
+        <v>49900</v>
       </c>
       <c r="G95">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B96" s="5">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="C96" t="s">
         <v>99</v>
@@ -9063,18 +9145,18 @@
         <v>66</v>
       </c>
       <c r="E96" t="s">
-        <v>1797</v>
-      </c>
-      <c r="F96" s="8">
-        <v>34900</v>
+        <v>1884</v>
+      </c>
+      <c r="F96" s="7">
+        <v>44700</v>
       </c>
       <c r="G96">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B97" s="5">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="C97" t="s">
         <v>99</v>
@@ -9083,18 +9165,18 @@
         <v>66</v>
       </c>
       <c r="E97" t="s">
-        <v>1806</v>
-      </c>
-      <c r="F97" s="8">
-        <v>34900</v>
+        <v>1865</v>
+      </c>
+      <c r="F97" s="7">
+        <v>556500</v>
       </c>
       <c r="G97">
-        <v>5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="98" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B98" s="5">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="C98" t="s">
         <v>99</v>
@@ -9103,18 +9185,18 @@
         <v>66</v>
       </c>
       <c r="E98" t="s">
-        <v>1939</v>
-      </c>
-      <c r="F98" s="8">
-        <v>202300</v>
+        <v>1937</v>
+      </c>
+      <c r="F98" s="7">
+        <v>954000</v>
       </c>
       <c r="G98">
-        <v>7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="99" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B99" s="5">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="C99" t="s">
         <v>99</v>
@@ -9123,18 +9205,18 @@
         <v>66</v>
       </c>
       <c r="E99" t="s">
-        <v>1913</v>
-      </c>
-      <c r="F99" s="8">
-        <v>516800</v>
+        <v>1851</v>
+      </c>
+      <c r="F99" s="7">
+        <v>64500</v>
       </c>
       <c r="G99">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B100" s="5">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="C100" t="s">
         <v>99</v>
@@ -9143,18 +9225,18 @@
         <v>66</v>
       </c>
       <c r="E100" t="s">
-        <v>1906</v>
-      </c>
-      <c r="F100" s="8">
-        <v>70700</v>
+        <v>1859</v>
+      </c>
+      <c r="F100" s="7">
+        <v>38700</v>
       </c>
       <c r="G100">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B101" s="5">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="C101" t="s">
         <v>99</v>
@@ -9163,18 +9245,18 @@
         <v>66</v>
       </c>
       <c r="E101" t="s">
-        <v>1924</v>
-      </c>
-      <c r="F101" s="8">
-        <v>228800</v>
+        <v>1867</v>
+      </c>
+      <c r="F101" s="7">
+        <v>231200</v>
       </c>
       <c r="G101">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="102" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B102" s="5">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="C102" t="s">
         <v>99</v>
@@ -9183,10 +9265,10 @@
         <v>66</v>
       </c>
       <c r="E102" t="s">
-        <v>1925</v>
-      </c>
-      <c r="F102" s="8">
-        <v>114400</v>
+        <v>1797</v>
+      </c>
+      <c r="F102" s="7">
+        <v>34900</v>
       </c>
       <c r="G102">
         <v>5</v>
@@ -9194,7 +9276,7 @@
     </row>
     <row r="103" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B103" s="5">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="C103" t="s">
         <v>99</v>
@@ -9203,10 +9285,10 @@
         <v>66</v>
       </c>
       <c r="E103" t="s">
-        <v>1926</v>
-      </c>
-      <c r="F103" s="8">
-        <v>74800</v>
+        <v>1806</v>
+      </c>
+      <c r="F103" s="7">
+        <v>34900</v>
       </c>
       <c r="G103">
         <v>5</v>
@@ -9214,7 +9296,7 @@
     </row>
     <row r="104" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B104" s="5">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="C104" t="s">
         <v>99</v>
@@ -9223,10 +9305,10 @@
         <v>66</v>
       </c>
       <c r="E104" t="s">
-        <v>1923</v>
-      </c>
-      <c r="F104" s="8">
-        <v>149660</v>
+        <v>1939</v>
+      </c>
+      <c r="F104" s="7">
+        <v>202300</v>
       </c>
       <c r="G104">
         <v>7</v>
@@ -9234,7 +9316,7 @@
     </row>
     <row r="105" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B105" s="5">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="C105" t="s">
         <v>99</v>
@@ -9243,18 +9325,18 @@
         <v>66</v>
       </c>
       <c r="E105" t="s">
-        <v>1800</v>
-      </c>
-      <c r="F105" s="8">
-        <v>104700</v>
+        <v>1913</v>
+      </c>
+      <c r="F105" s="7">
+        <v>516800</v>
       </c>
       <c r="G105">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="106" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B106" s="5">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="C106" t="s">
         <v>99</v>
@@ -9263,18 +9345,18 @@
         <v>66</v>
       </c>
       <c r="E106" t="s">
-        <v>1947</v>
-      </c>
-      <c r="F106" s="8">
-        <v>945000</v>
+        <v>1906</v>
+      </c>
+      <c r="F106" s="7">
+        <v>70700</v>
       </c>
       <c r="G106">
-        <v>50</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B107" s="5">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="C107" t="s">
         <v>99</v>
@@ -9283,18 +9365,18 @@
         <v>66</v>
       </c>
       <c r="E107" t="s">
-        <v>1930</v>
-      </c>
-      <c r="F107" s="8">
-        <v>582300</v>
+        <v>1924</v>
+      </c>
+      <c r="F107" s="7">
+        <v>228800</v>
       </c>
       <c r="G107">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="108" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B108" s="5">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="C108" t="s">
         <v>99</v>
@@ -9303,18 +9385,18 @@
         <v>66</v>
       </c>
       <c r="E108" t="s">
-        <v>1931</v>
-      </c>
-      <c r="F108" s="8">
-        <v>582300</v>
+        <v>1925</v>
+      </c>
+      <c r="F108" s="7">
+        <v>114400</v>
       </c>
       <c r="G108">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B109" s="5">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="C109" t="s">
         <v>99</v>
@@ -9323,18 +9405,18 @@
         <v>66</v>
       </c>
       <c r="E109" t="s">
-        <v>1932</v>
-      </c>
-      <c r="F109" s="8">
-        <v>954000</v>
+        <v>1926</v>
+      </c>
+      <c r="F109" s="7">
+        <v>74800</v>
       </c>
       <c r="G109">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B110" s="5">
-        <v>46143</v>
+        <v>46082</v>
       </c>
       <c r="C110" t="s">
         <v>99</v>
@@ -9343,18 +9425,18 @@
         <v>66</v>
       </c>
       <c r="E110" t="s">
-        <v>1884</v>
-      </c>
-      <c r="F110" s="8">
-        <v>44700</v>
+        <v>1923</v>
+      </c>
+      <c r="F110" s="7">
+        <v>149660</v>
       </c>
       <c r="G110">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="111" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B111" s="5">
-        <v>46143</v>
+        <v>46082</v>
       </c>
       <c r="C111" t="s">
         <v>99</v>
@@ -9363,18 +9445,18 @@
         <v>66</v>
       </c>
       <c r="E111" t="s">
-        <v>1865</v>
-      </c>
-      <c r="F111" s="8">
-        <v>397500</v>
+        <v>1800</v>
+      </c>
+      <c r="F111" s="7">
+        <v>104700</v>
       </c>
       <c r="G111">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B112" s="5">
-        <v>46143</v>
+        <v>46082</v>
       </c>
       <c r="C112" t="s">
         <v>99</v>
@@ -9383,18 +9465,18 @@
         <v>66</v>
       </c>
       <c r="E112" t="s">
-        <v>1937</v>
-      </c>
-      <c r="F112" s="8">
-        <v>954000</v>
+        <v>1947</v>
+      </c>
+      <c r="F112" s="7">
+        <v>756000</v>
       </c>
       <c r="G112">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="113" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B113" s="5">
-        <v>46143</v>
+        <v>46082</v>
       </c>
       <c r="C113" t="s">
         <v>99</v>
@@ -9403,18 +9485,18 @@
         <v>66</v>
       </c>
       <c r="E113" t="s">
-        <v>1851</v>
-      </c>
-      <c r="F113" s="8">
-        <v>64500</v>
+        <v>1930</v>
+      </c>
+      <c r="F113" s="7">
+        <v>388200</v>
       </c>
       <c r="G113">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="114" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B114" s="5">
-        <v>46143</v>
+        <v>46082</v>
       </c>
       <c r="C114" t="s">
         <v>99</v>
@@ -9423,18 +9505,18 @@
         <v>66</v>
       </c>
       <c r="E114" t="s">
-        <v>1859</v>
-      </c>
-      <c r="F114" s="8">
-        <v>38700</v>
+        <v>1931</v>
+      </c>
+      <c r="F114" s="7">
+        <v>388200</v>
       </c>
       <c r="G114">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="115" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B115" s="5">
-        <v>46143</v>
+        <v>46082</v>
       </c>
       <c r="C115" t="s">
         <v>99</v>
@@ -9443,18 +9525,18 @@
         <v>66</v>
       </c>
       <c r="E115" t="s">
-        <v>1867</v>
-      </c>
-      <c r="F115" s="8">
-        <v>231200</v>
+        <v>1932</v>
+      </c>
+      <c r="F115" s="7">
+        <v>636000</v>
       </c>
       <c r="G115">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="116" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B116" s="5">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="C116" t="s">
         <v>99</v>
@@ -9463,18 +9545,18 @@
         <v>66</v>
       </c>
       <c r="E116" t="s">
-        <v>1797</v>
-      </c>
-      <c r="F116" s="8">
-        <v>34900</v>
+        <v>1884</v>
+      </c>
+      <c r="F116" s="7">
+        <v>44700</v>
       </c>
       <c r="G116">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B117" s="5">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="C117" t="s">
         <v>99</v>
@@ -9483,18 +9565,18 @@
         <v>66</v>
       </c>
       <c r="E117" t="s">
-        <v>1806</v>
-      </c>
-      <c r="F117" s="8">
-        <v>34900</v>
+        <v>1865</v>
+      </c>
+      <c r="F117" s="7">
+        <v>795000</v>
       </c>
       <c r="G117">
-        <v>5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="118" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B118" s="5">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="C118" t="s">
         <v>99</v>
@@ -9503,18 +9585,18 @@
         <v>66</v>
       </c>
       <c r="E118" t="s">
-        <v>1939</v>
-      </c>
-      <c r="F118" s="8">
-        <v>202300</v>
+        <v>1937</v>
+      </c>
+      <c r="F118" s="7">
+        <v>1272000</v>
       </c>
       <c r="G118">
-        <v>7</v>
+        <v>80</v>
       </c>
     </row>
     <row r="119" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B119" s="5">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="C119" t="s">
         <v>99</v>
@@ -9523,18 +9605,18 @@
         <v>66</v>
       </c>
       <c r="E119" t="s">
-        <v>1913</v>
-      </c>
-      <c r="F119" s="8">
-        <v>516800</v>
+        <v>1851</v>
+      </c>
+      <c r="F119" s="7">
+        <v>64500</v>
       </c>
       <c r="G119">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B120" s="5">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="C120" t="s">
         <v>99</v>
@@ -9543,18 +9625,18 @@
         <v>66</v>
       </c>
       <c r="E120" t="s">
-        <v>1906</v>
-      </c>
-      <c r="F120" s="8">
-        <v>70700</v>
+        <v>1859</v>
+      </c>
+      <c r="F120" s="7">
+        <v>38700</v>
       </c>
       <c r="G120">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B121" s="5">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="C121" t="s">
         <v>99</v>
@@ -9563,18 +9645,18 @@
         <v>66</v>
       </c>
       <c r="E121" t="s">
-        <v>1924</v>
-      </c>
-      <c r="F121" s="8">
-        <v>228800</v>
+        <v>1867</v>
+      </c>
+      <c r="F121" s="7">
+        <v>231200</v>
       </c>
       <c r="G121">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="122" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B122" s="5">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="C122" t="s">
         <v>99</v>
@@ -9583,10 +9665,10 @@
         <v>66</v>
       </c>
       <c r="E122" t="s">
-        <v>1925</v>
-      </c>
-      <c r="F122" s="8">
-        <v>114400</v>
+        <v>1797</v>
+      </c>
+      <c r="F122" s="7">
+        <v>34900</v>
       </c>
       <c r="G122">
         <v>5</v>
@@ -9594,7 +9676,7 @@
     </row>
     <row r="123" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B123" s="5">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="C123" t="s">
         <v>99</v>
@@ -9603,10 +9685,10 @@
         <v>66</v>
       </c>
       <c r="E123" t="s">
-        <v>1926</v>
-      </c>
-      <c r="F123" s="8">
-        <v>74800</v>
+        <v>1806</v>
+      </c>
+      <c r="F123" s="7">
+        <v>34900</v>
       </c>
       <c r="G123">
         <v>5</v>
@@ -9614,7 +9696,7 @@
     </row>
     <row r="124" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B124" s="5">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="C124" t="s">
         <v>99</v>
@@ -9623,10 +9705,10 @@
         <v>66</v>
       </c>
       <c r="E124" t="s">
-        <v>1923</v>
-      </c>
-      <c r="F124" s="8">
-        <v>149660</v>
+        <v>1939</v>
+      </c>
+      <c r="F124" s="7">
+        <v>202300</v>
       </c>
       <c r="G124">
         <v>7</v>
@@ -9634,7 +9716,7 @@
     </row>
     <row r="125" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B125" s="5">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="C125" t="s">
         <v>99</v>
@@ -9643,18 +9725,18 @@
         <v>66</v>
       </c>
       <c r="E125" t="s">
-        <v>1800</v>
-      </c>
-      <c r="F125" s="8">
-        <v>104700</v>
+        <v>1913</v>
+      </c>
+      <c r="F125" s="7">
+        <v>516800</v>
       </c>
       <c r="G125">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="126" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B126" s="5">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="C126" t="s">
         <v>99</v>
@@ -9663,18 +9745,18 @@
         <v>66</v>
       </c>
       <c r="E126" t="s">
-        <v>1947</v>
-      </c>
-      <c r="F126" s="8">
-        <v>1134000</v>
+        <v>1906</v>
+      </c>
+      <c r="F126" s="7">
+        <v>70700</v>
       </c>
       <c r="G126">
-        <v>60</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B127" s="5">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="C127" t="s">
         <v>99</v>
@@ -9683,18 +9765,18 @@
         <v>66</v>
       </c>
       <c r="E127" t="s">
-        <v>1930</v>
-      </c>
-      <c r="F127" s="8">
-        <v>582300</v>
+        <v>1924</v>
+      </c>
+      <c r="F127" s="7">
+        <v>228800</v>
       </c>
       <c r="G127">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="128" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B128" s="5">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="C128" t="s">
         <v>99</v>
@@ -9703,18 +9785,18 @@
         <v>66</v>
       </c>
       <c r="E128" t="s">
-        <v>1931</v>
-      </c>
-      <c r="F128" s="8">
-        <v>582300</v>
+        <v>1925</v>
+      </c>
+      <c r="F128" s="7">
+        <v>114400</v>
       </c>
       <c r="G128">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B129" s="5">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="C129" t="s">
         <v>99</v>
@@ -9723,18 +9805,18 @@
         <v>66</v>
       </c>
       <c r="E129" t="s">
-        <v>1932</v>
-      </c>
-      <c r="F129" s="8">
-        <v>954000</v>
+        <v>1926</v>
+      </c>
+      <c r="F129" s="7">
+        <v>74800</v>
       </c>
       <c r="G129">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B130" s="5">
-        <v>46174</v>
+        <v>46113</v>
       </c>
       <c r="C130" t="s">
         <v>99</v>
@@ -9743,18 +9825,18 @@
         <v>66</v>
       </c>
       <c r="E130" t="s">
-        <v>1884</v>
-      </c>
-      <c r="F130" s="8">
-        <v>44700</v>
+        <v>1923</v>
+      </c>
+      <c r="F130" s="7">
+        <v>149660</v>
       </c>
       <c r="G130">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="131" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B131" s="5">
-        <v>46174</v>
+        <v>46113</v>
       </c>
       <c r="C131" t="s">
         <v>99</v>
@@ -9763,18 +9845,18 @@
         <v>66</v>
       </c>
       <c r="E131" t="s">
-        <v>1865</v>
-      </c>
-      <c r="F131" s="8">
-        <v>397500</v>
+        <v>1800</v>
+      </c>
+      <c r="F131" s="7">
+        <v>104700</v>
       </c>
       <c r="G131">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B132" s="5">
-        <v>46174</v>
+        <v>46113</v>
       </c>
       <c r="C132" t="s">
         <v>99</v>
@@ -9783,18 +9865,18 @@
         <v>66</v>
       </c>
       <c r="E132" t="s">
-        <v>1937</v>
-      </c>
-      <c r="F132" s="8">
-        <v>954000</v>
+        <v>1947</v>
+      </c>
+      <c r="F132" s="7">
+        <v>945000</v>
       </c>
       <c r="G132">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="133" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B133" s="5">
-        <v>46174</v>
+        <v>46113</v>
       </c>
       <c r="C133" t="s">
         <v>99</v>
@@ -9803,18 +9885,18 @@
         <v>66</v>
       </c>
       <c r="E133" t="s">
-        <v>1851</v>
-      </c>
-      <c r="F133" s="8">
-        <v>64500</v>
+        <v>1930</v>
+      </c>
+      <c r="F133" s="7">
+        <v>582300</v>
       </c>
       <c r="G133">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="134" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B134" s="5">
-        <v>46174</v>
+        <v>46113</v>
       </c>
       <c r="C134" t="s">
         <v>99</v>
@@ -9823,18 +9905,18 @@
         <v>66</v>
       </c>
       <c r="E134" t="s">
-        <v>1859</v>
-      </c>
-      <c r="F134" s="8">
-        <v>38700</v>
+        <v>1931</v>
+      </c>
+      <c r="F134" s="7">
+        <v>582300</v>
       </c>
       <c r="G134">
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="135" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B135" s="5">
-        <v>46174</v>
+        <v>46113</v>
       </c>
       <c r="C135" t="s">
         <v>99</v>
@@ -9843,18 +9925,18 @@
         <v>66</v>
       </c>
       <c r="E135" t="s">
-        <v>1867</v>
-      </c>
-      <c r="F135" s="8">
-        <v>231200</v>
+        <v>1932</v>
+      </c>
+      <c r="F135" s="7">
+        <v>954000</v>
       </c>
       <c r="G135">
-        <v>8</v>
+        <v>30</v>
       </c>
     </row>
     <row r="136" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B136" s="5">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="C136" t="s">
         <v>99</v>
@@ -9863,18 +9945,18 @@
         <v>66</v>
       </c>
       <c r="E136" t="s">
-        <v>1797</v>
-      </c>
-      <c r="F136" s="8">
-        <v>34900</v>
+        <v>1884</v>
+      </c>
+      <c r="F136" s="7">
+        <v>44700</v>
       </c>
       <c r="G136">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="137" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B137" s="5">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="C137" t="s">
         <v>99</v>
@@ -9883,18 +9965,18 @@
         <v>66</v>
       </c>
       <c r="E137" t="s">
-        <v>1806</v>
-      </c>
-      <c r="F137" s="8">
-        <v>34900</v>
+        <v>1865</v>
+      </c>
+      <c r="F137" s="7">
+        <v>397500</v>
       </c>
       <c r="G137">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="138" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B138" s="5">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="C138" t="s">
         <v>99</v>
@@ -9903,18 +9985,18 @@
         <v>66</v>
       </c>
       <c r="E138" t="s">
-        <v>1939</v>
-      </c>
-      <c r="F138" s="8">
-        <v>202300</v>
+        <v>1937</v>
+      </c>
+      <c r="F138" s="7">
+        <v>954000</v>
       </c>
       <c r="G138">
-        <v>7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="139" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B139" s="5">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="C139" t="s">
         <v>99</v>
@@ -9923,18 +10005,18 @@
         <v>66</v>
       </c>
       <c r="E139" t="s">
-        <v>1913</v>
-      </c>
-      <c r="F139" s="8">
-        <v>516800</v>
+        <v>1851</v>
+      </c>
+      <c r="F139" s="7">
+        <v>64500</v>
       </c>
       <c r="G139">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B140" s="5">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="C140" t="s">
         <v>99</v>
@@ -9943,18 +10025,18 @@
         <v>66</v>
       </c>
       <c r="E140" t="s">
-        <v>1906</v>
-      </c>
-      <c r="F140" s="8">
-        <v>70700</v>
+        <v>1859</v>
+      </c>
+      <c r="F140" s="7">
+        <v>38700</v>
       </c>
       <c r="G140">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="141" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B141" s="5">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="C141" t="s">
         <v>99</v>
@@ -9963,18 +10045,18 @@
         <v>66</v>
       </c>
       <c r="E141" t="s">
-        <v>1924</v>
-      </c>
-      <c r="F141" s="8">
-        <v>228800</v>
+        <v>1867</v>
+      </c>
+      <c r="F141" s="7">
+        <v>231200</v>
       </c>
       <c r="G141">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="142" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B142" s="5">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="C142" t="s">
         <v>99</v>
@@ -9983,10 +10065,10 @@
         <v>66</v>
       </c>
       <c r="E142" t="s">
-        <v>1925</v>
-      </c>
-      <c r="F142" s="8">
-        <v>114400</v>
+        <v>1797</v>
+      </c>
+      <c r="F142" s="7">
+        <v>34900</v>
       </c>
       <c r="G142">
         <v>5</v>
@@ -9994,7 +10076,7 @@
     </row>
     <row r="143" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B143" s="5">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="C143" t="s">
         <v>99</v>
@@ -10003,10 +10085,10 @@
         <v>66</v>
       </c>
       <c r="E143" t="s">
-        <v>1926</v>
-      </c>
-      <c r="F143" s="8">
-        <v>74800</v>
+        <v>1806</v>
+      </c>
+      <c r="F143" s="7">
+        <v>34900</v>
       </c>
       <c r="G143">
         <v>5</v>
@@ -10014,7 +10096,7 @@
     </row>
     <row r="144" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B144" s="5">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="C144" t="s">
         <v>99</v>
@@ -10023,18 +10105,18 @@
         <v>66</v>
       </c>
       <c r="E144" t="s">
-        <v>1923</v>
-      </c>
-      <c r="F144" s="8">
-        <v>149660</v>
+        <v>1939</v>
+      </c>
+      <c r="F144" s="7">
+        <v>202300</v>
       </c>
       <c r="G144">
         <v>7</v>
       </c>
     </row>
-    <row r="145" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="145" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B145" s="5">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="C145" t="s">
         <v>99</v>
@@ -10043,18 +10125,18 @@
         <v>66</v>
       </c>
       <c r="E145" t="s">
-        <v>1800</v>
-      </c>
-      <c r="F145" s="8">
-        <v>104700</v>
+        <v>1913</v>
+      </c>
+      <c r="F145" s="7">
+        <v>516800</v>
       </c>
       <c r="G145">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="146" spans="2:8" x14ac:dyDescent="0.45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="146" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B146" s="5">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="C146" t="s">
         <v>99</v>
@@ -10063,18 +10145,18 @@
         <v>66</v>
       </c>
       <c r="E146" t="s">
-        <v>1947</v>
-      </c>
-      <c r="F146" s="8">
-        <v>1134000</v>
+        <v>1906</v>
+      </c>
+      <c r="F146" s="7">
+        <v>70700</v>
       </c>
       <c r="G146">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="147" spans="2:8" x14ac:dyDescent="0.45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B147" s="5">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="C147" t="s">
         <v>99</v>
@@ -10083,18 +10165,18 @@
         <v>66</v>
       </c>
       <c r="E147" t="s">
-        <v>1930</v>
-      </c>
-      <c r="F147" s="8">
-        <v>582300</v>
+        <v>1924</v>
+      </c>
+      <c r="F147" s="7">
+        <v>228800</v>
       </c>
       <c r="G147">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="148" spans="2:8" x14ac:dyDescent="0.45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="148" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B148" s="5">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="C148" t="s">
         <v>99</v>
@@ -10103,18 +10185,18 @@
         <v>66</v>
       </c>
       <c r="E148" t="s">
-        <v>1931</v>
-      </c>
-      <c r="F148" s="8">
-        <v>582300</v>
+        <v>1925</v>
+      </c>
+      <c r="F148" s="7">
+        <v>114400</v>
       </c>
       <c r="G148">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="149" spans="2:8" x14ac:dyDescent="0.45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="149" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B149" s="5">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="C149" t="s">
         <v>99</v>
@@ -10123,614 +10205,536 @@
         <v>66</v>
       </c>
       <c r="E149" t="s">
-        <v>1932</v>
-      </c>
-      <c r="F149" s="8">
-        <v>954000</v>
+        <v>1926</v>
+      </c>
+      <c r="F149" s="7">
+        <v>74800</v>
       </c>
       <c r="G149">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="150" spans="2:8" x14ac:dyDescent="0.45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="150" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B150" s="5">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="C150" t="s">
         <v>99</v>
       </c>
       <c r="D150" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E150" t="s">
-        <v>1884</v>
-      </c>
-      <c r="F150" s="8">
-        <v>462000</v>
+        <v>1923</v>
+      </c>
+      <c r="F150" s="7">
+        <v>149660</v>
       </c>
       <c r="G150">
-        <v>30</v>
-      </c>
-      <c r="H150" t="s">
-        <v>2221</v>
-      </c>
-    </row>
-    <row r="151" spans="2:8" x14ac:dyDescent="0.45">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="151" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B151" s="5">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="C151" t="s">
         <v>99</v>
       </c>
       <c r="D151" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E151" t="s">
-        <v>1859</v>
-      </c>
-      <c r="F151" s="8">
-        <v>810000</v>
+        <v>1800</v>
+      </c>
+      <c r="F151" s="7">
+        <v>104700</v>
       </c>
       <c r="G151">
-        <v>60</v>
-      </c>
-      <c r="H151" t="s">
-        <v>2221</v>
-      </c>
-    </row>
-    <row r="152" spans="2:8" x14ac:dyDescent="0.45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="152" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B152" s="5">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="C152" t="s">
         <v>99</v>
       </c>
       <c r="D152" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E152" t="s">
-        <v>1797</v>
-      </c>
-      <c r="F152" s="8">
-        <v>225000</v>
+        <v>1947</v>
+      </c>
+      <c r="F152" s="7">
+        <v>1134000</v>
       </c>
       <c r="G152">
-        <v>30</v>
-      </c>
-      <c r="H152" t="s">
-        <v>2221</v>
-      </c>
-    </row>
-    <row r="153" spans="2:8" x14ac:dyDescent="0.45">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="153" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B153" s="5">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="C153" t="s">
         <v>99</v>
       </c>
       <c r="D153" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E153" t="s">
-        <v>1806</v>
-      </c>
-      <c r="F153" s="8">
-        <v>225000</v>
+        <v>1930</v>
+      </c>
+      <c r="F153" s="7">
+        <v>582300</v>
       </c>
       <c r="G153">
-        <v>30</v>
-      </c>
-      <c r="H153" t="s">
-        <v>2221</v>
-      </c>
-    </row>
-    <row r="154" spans="2:8" x14ac:dyDescent="0.45">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="154" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B154" s="5">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="C154" t="s">
         <v>99</v>
       </c>
       <c r="D154" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E154" t="s">
-        <v>1936</v>
-      </c>
-      <c r="F154" s="8">
-        <v>3024000</v>
+        <v>1931</v>
+      </c>
+      <c r="F154" s="7">
+        <v>582300</v>
       </c>
       <c r="G154">
-        <v>160</v>
-      </c>
-      <c r="H154" t="s">
-        <v>2221</v>
-      </c>
-    </row>
-    <row r="155" spans="2:8" x14ac:dyDescent="0.45">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="155" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B155" s="5">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="C155" t="s">
         <v>99</v>
       </c>
       <c r="D155" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E155" t="s">
-        <v>1889</v>
-      </c>
-      <c r="F155" s="8">
-        <v>194400</v>
+        <v>1932</v>
+      </c>
+      <c r="F155" s="7">
+        <v>954000</v>
       </c>
       <c r="G155">
         <v>30</v>
       </c>
-      <c r="H155" t="s">
-        <v>2221</v>
-      </c>
-    </row>
-    <row r="156" spans="2:8" x14ac:dyDescent="0.45">
+    </row>
+    <row r="156" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B156" s="5">
-        <v>46113</v>
+        <v>46174</v>
       </c>
       <c r="C156" t="s">
         <v>99</v>
       </c>
       <c r="D156" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E156" t="s">
-        <v>2047</v>
-      </c>
-      <c r="F156" s="8">
-        <v>453600</v>
+        <v>1884</v>
+      </c>
+      <c r="F156" s="7">
+        <v>44700</v>
       </c>
       <c r="G156">
-        <v>70</v>
-      </c>
-      <c r="H156" t="s">
-        <v>2221</v>
-      </c>
-    </row>
-    <row r="157" spans="2:8" x14ac:dyDescent="0.45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="157" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B157" s="5">
-        <v>46113</v>
+        <v>46174</v>
       </c>
       <c r="C157" t="s">
         <v>99</v>
       </c>
       <c r="D157" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E157" t="s">
-        <v>2048</v>
-      </c>
-      <c r="F157" s="8">
-        <v>453600</v>
+        <v>1865</v>
+      </c>
+      <c r="F157" s="7">
+        <v>397500</v>
       </c>
       <c r="G157">
-        <v>70</v>
-      </c>
-      <c r="H157" t="s">
-        <v>2221</v>
-      </c>
-    </row>
-    <row r="158" spans="2:8" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="158" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B158" s="5">
-        <v>46113</v>
+        <v>46174</v>
       </c>
       <c r="C158" t="s">
         <v>99</v>
       </c>
       <c r="D158" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E158" t="s">
-        <v>1965</v>
-      </c>
-      <c r="F158" s="8">
-        <v>453600</v>
+        <v>1937</v>
+      </c>
+      <c r="F158" s="7">
+        <v>954000</v>
       </c>
       <c r="G158">
-        <v>70</v>
-      </c>
-      <c r="H158" t="s">
-        <v>2221</v>
-      </c>
-    </row>
-    <row r="159" spans="2:8" x14ac:dyDescent="0.45">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="159" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B159" s="5">
-        <v>46113</v>
+        <v>46174</v>
       </c>
       <c r="C159" t="s">
         <v>99</v>
       </c>
       <c r="D159" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E159" t="s">
-        <v>1859</v>
-      </c>
-      <c r="F159" s="8">
-        <v>2700000</v>
+        <v>1851</v>
+      </c>
+      <c r="F159" s="7">
+        <v>64500</v>
       </c>
       <c r="G159">
-        <v>200</v>
-      </c>
-      <c r="H159" t="s">
-        <v>2222</v>
-      </c>
-    </row>
-    <row r="160" spans="2:8" x14ac:dyDescent="0.45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="160" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B160" s="5">
-        <v>46113</v>
+        <v>46174</v>
       </c>
       <c r="C160" t="s">
         <v>99</v>
       </c>
       <c r="D160" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E160" t="s">
-        <v>1797</v>
-      </c>
-      <c r="F160" s="8">
-        <v>1350000</v>
+        <v>1859</v>
+      </c>
+      <c r="F160" s="7">
+        <v>38700</v>
       </c>
       <c r="G160">
-        <v>180</v>
-      </c>
-      <c r="H160" t="s">
-        <v>2222</v>
-      </c>
-    </row>
-    <row r="161" spans="2:8" x14ac:dyDescent="0.45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="161" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B161" s="5">
-        <v>46113</v>
+        <v>46174</v>
       </c>
       <c r="C161" t="s">
         <v>99</v>
       </c>
       <c r="D161" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E161" t="s">
-        <v>1806</v>
-      </c>
-      <c r="F161" s="8">
-        <v>1050000</v>
+        <v>1867</v>
+      </c>
+      <c r="F161" s="7">
+        <v>231200</v>
       </c>
       <c r="G161">
-        <v>140</v>
-      </c>
-      <c r="H161" t="s">
-        <v>2222</v>
-      </c>
-    </row>
-    <row r="162" spans="2:8" x14ac:dyDescent="0.45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="162" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B162" s="5">
-        <v>46113</v>
+        <v>46174</v>
       </c>
       <c r="C162" t="s">
         <v>99</v>
       </c>
       <c r="D162" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E162" t="s">
-        <v>1936</v>
-      </c>
-      <c r="F162" s="8">
-        <v>3402000</v>
+        <v>1797</v>
+      </c>
+      <c r="F162" s="7">
+        <v>34900</v>
       </c>
       <c r="G162">
-        <v>180</v>
-      </c>
-      <c r="H162" t="s">
-        <v>2222</v>
-      </c>
-    </row>
-    <row r="163" spans="2:8" x14ac:dyDescent="0.45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="163" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B163" s="5">
-        <v>46113</v>
+        <v>46174</v>
       </c>
       <c r="C163" t="s">
         <v>99</v>
       </c>
       <c r="D163" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E163" t="s">
-        <v>2047</v>
-      </c>
-      <c r="F163" s="8">
-        <v>1296000</v>
+        <v>1806</v>
+      </c>
+      <c r="F163" s="7">
+        <v>34900</v>
       </c>
       <c r="G163">
-        <v>200</v>
-      </c>
-      <c r="H163" t="s">
-        <v>2222</v>
-      </c>
-    </row>
-    <row r="164" spans="2:8" x14ac:dyDescent="0.45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="164" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B164" s="5">
-        <v>46113</v>
+        <v>46174</v>
       </c>
       <c r="C164" t="s">
         <v>99</v>
       </c>
       <c r="D164" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E164" t="s">
-        <v>2048</v>
-      </c>
-      <c r="F164" s="8">
-        <v>1296000</v>
+        <v>1939</v>
+      </c>
+      <c r="F164" s="7">
+        <v>202300</v>
       </c>
       <c r="G164">
-        <v>200</v>
-      </c>
-      <c r="H164" t="s">
-        <v>2222</v>
-      </c>
-    </row>
-    <row r="165" spans="2:8" x14ac:dyDescent="0.45">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="165" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B165" s="5">
-        <v>46113</v>
+        <v>46174</v>
       </c>
       <c r="C165" t="s">
         <v>99</v>
       </c>
       <c r="D165" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E165" t="s">
-        <v>1965</v>
-      </c>
-      <c r="F165" s="8">
-        <v>1296000</v>
+        <v>1913</v>
+      </c>
+      <c r="F165" s="7">
+        <v>516800</v>
       </c>
       <c r="G165">
-        <v>200</v>
-      </c>
-      <c r="H165" t="s">
-        <v>2222</v>
-      </c>
-    </row>
-    <row r="166" spans="2:8" x14ac:dyDescent="0.45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="166" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B166" s="5">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="C166" t="s">
         <v>99</v>
       </c>
       <c r="D166" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E166" t="s">
-        <v>1851</v>
-      </c>
-      <c r="F166" s="8">
-        <v>135000</v>
+        <v>1906</v>
+      </c>
+      <c r="F166" s="7">
+        <v>70700</v>
       </c>
       <c r="G166">
-        <v>10</v>
-      </c>
-      <c r="H166" t="s">
-        <v>2221</v>
-      </c>
-    </row>
-    <row r="167" spans="2:8" x14ac:dyDescent="0.45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B167" s="5">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="C167" t="s">
         <v>99</v>
       </c>
       <c r="D167" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E167" t="s">
-        <v>2223</v>
-      </c>
-      <c r="F167" s="8">
-        <v>300000</v>
+        <v>1924</v>
+      </c>
+      <c r="F167" s="7">
+        <v>228800</v>
       </c>
       <c r="G167">
-        <v>50</v>
-      </c>
-      <c r="H167" t="s">
-        <v>2221</v>
-      </c>
-    </row>
-    <row r="168" spans="2:8" x14ac:dyDescent="0.45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="168" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B168" s="5">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="C168" t="s">
         <v>99</v>
       </c>
       <c r="D168" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E168" t="s">
-        <v>2224</v>
-      </c>
-      <c r="F168" s="8">
-        <v>150000</v>
+        <v>1925</v>
+      </c>
+      <c r="F168" s="7">
+        <v>114400</v>
       </c>
       <c r="G168">
-        <v>25</v>
-      </c>
-      <c r="H168" t="s">
-        <v>2221</v>
-      </c>
-    </row>
-    <row r="169" spans="2:8" x14ac:dyDescent="0.45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="169" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B169" s="5">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="C169" t="s">
         <v>99</v>
       </c>
       <c r="D169" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E169" t="s">
-        <v>1843</v>
-      </c>
-      <c r="F169" s="8">
-        <v>247500</v>
+        <v>1926</v>
+      </c>
+      <c r="F169" s="7">
+        <v>74800</v>
       </c>
       <c r="G169">
         <v>5</v>
       </c>
-      <c r="H169" t="s">
-        <v>2221</v>
-      </c>
-    </row>
-    <row r="170" spans="2:8" x14ac:dyDescent="0.45">
+    </row>
+    <row r="170" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B170" s="5">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="C170" t="s">
         <v>99</v>
       </c>
       <c r="D170" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E170" t="s">
-        <v>1781</v>
-      </c>
-      <c r="F170" s="8">
-        <v>157500</v>
+        <v>1923</v>
+      </c>
+      <c r="F170" s="7">
+        <v>149660</v>
       </c>
       <c r="G170">
-        <v>5</v>
-      </c>
-      <c r="H170" t="s">
-        <v>2221</v>
-      </c>
-    </row>
-    <row r="171" spans="2:8" x14ac:dyDescent="0.45">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="171" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B171" s="5">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="C171" t="s">
         <v>99</v>
       </c>
       <c r="D171" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E171" t="s">
-        <v>2046</v>
-      </c>
-      <c r="F171" s="8">
-        <v>94500</v>
+        <v>1800</v>
+      </c>
+      <c r="F171" s="7">
+        <v>104700</v>
       </c>
       <c r="G171">
-        <v>3</v>
-      </c>
-      <c r="H171" t="s">
-        <v>2221</v>
-      </c>
-    </row>
-    <row r="172" spans="2:8" x14ac:dyDescent="0.45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="172" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B172" s="5">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="C172" t="s">
         <v>99</v>
       </c>
       <c r="D172" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E172" t="s">
-        <v>1923</v>
-      </c>
-      <c r="F172" s="8">
-        <v>437600</v>
+        <v>1947</v>
+      </c>
+      <c r="F172" s="7">
+        <v>1134000</v>
       </c>
       <c r="G172">
-        <v>20</v>
-      </c>
-      <c r="H172" t="s">
-        <v>2221</v>
-      </c>
-    </row>
-    <row r="173" spans="2:8" x14ac:dyDescent="0.45">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="173" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B173" s="5">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="C173" t="s">
         <v>99</v>
       </c>
       <c r="D173" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E173" t="s">
-        <v>1851</v>
-      </c>
-      <c r="F173" s="8">
-        <v>337500</v>
+        <v>1930</v>
+      </c>
+      <c r="F173" s="7">
+        <v>582300</v>
       </c>
       <c r="G173">
-        <v>25</v>
-      </c>
-      <c r="H173" t="s">
-        <v>2222</v>
-      </c>
-    </row>
-    <row r="174" spans="2:8" x14ac:dyDescent="0.45">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="174" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B174" s="5">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="C174" t="s">
         <v>99</v>
       </c>
       <c r="D174" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E174" t="s">
-        <v>2223</v>
-      </c>
-      <c r="F174" s="8">
-        <v>960000</v>
+        <v>1931</v>
+      </c>
+      <c r="F174" s="7">
+        <v>582300</v>
       </c>
       <c r="G174">
-        <v>160</v>
-      </c>
-      <c r="H174" t="s">
-        <v>2222</v>
-      </c>
-    </row>
-    <row r="175" spans="2:8" x14ac:dyDescent="0.45">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="175" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B175" s="5">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="C175" t="s">
         <v>99</v>
       </c>
       <c r="D175" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E175" t="s">
-        <v>2224</v>
-      </c>
-      <c r="F175" s="8">
-        <v>1020000</v>
+        <v>1932</v>
+      </c>
+      <c r="F175" s="7">
+        <v>954000</v>
       </c>
       <c r="G175">
-        <v>170</v>
-      </c>
-      <c r="H175" t="s">
-        <v>2222</v>
-      </c>
-    </row>
-    <row r="176" spans="2:8" x14ac:dyDescent="0.45">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="176" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B176" s="5">
         <v>46082</v>
       </c>
@@ -10740,10 +10744,10 @@
       <c r="D176" t="s">
         <v>77</v>
       </c>
-      <c r="E176" s="9" t="s">
+      <c r="E176" s="8" t="s">
         <v>1827</v>
       </c>
-      <c r="F176" s="8">
+      <c r="F176" s="7">
         <v>2940000</v>
       </c>
       <c r="G176">
@@ -10760,10 +10764,10 @@
       <c r="D177" t="s">
         <v>77</v>
       </c>
-      <c r="E177" s="9" t="s">
+      <c r="E177" s="8" t="s">
         <v>1827</v>
       </c>
-      <c r="F177" s="8">
+      <c r="F177" s="7">
         <v>3675000</v>
       </c>
       <c r="G177">
@@ -10780,10 +10784,10 @@
       <c r="D178" t="s">
         <v>77</v>
       </c>
-      <c r="E178" s="9" t="s">
+      <c r="E178" s="8" t="s">
         <v>1827</v>
       </c>
-      <c r="F178" s="8">
+      <c r="F178" s="7">
         <v>2205000</v>
       </c>
       <c r="G178">
@@ -10800,10 +10804,10 @@
       <c r="D179" t="s">
         <v>77</v>
       </c>
-      <c r="E179" s="9" t="s">
+      <c r="E179" s="8" t="s">
         <v>1827</v>
       </c>
-      <c r="F179" s="8">
+      <c r="F179" s="7">
         <v>1960000</v>
       </c>
       <c r="G179">
@@ -10811,11 +10815,16 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H179" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H179">
+      <sortCondition ref="H1:H179"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="511" yWindow="550" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" xWindow="511" yWindow="550" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="목록에서 선택해주세요" prompt="채널을 선택하세요" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>목록!$A$1:$A$56</xm:f>
